--- a/GK11/Flightdata Übung.xlsx
+++ b/GK11/Flightdata Übung.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/957949413b80b056/Desktop/vova/INSY/GK11/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{B8ABED43-09B7-43A1-B683-80A162595F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F286FFE8-0BE6-436F-BC82-41784DB94739}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{B8ABED43-09B7-43A1-B683-80A162595F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CB68219-75A2-4A2D-9BDD-CB7D9CF332F0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0674F595-9AAF-41B8-A06B-E471226C5F68}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{0674F595-9AAF-41B8-A06B-E471226C5F68}"/>
   </bookViews>
   <sheets>
     <sheet name="Fragen" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="53">
   <si>
     <t>Nachname eines Passagiers der mit 'S' beginnt. Sein Vorname lautet 'Cadman'.</t>
   </si>
@@ -278,6 +278,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -761,7 +765,9 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B25" s="2"/>
+      <c r="B25" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
